--- a/Reports/vessel_construction_report.xlsx
+++ b/Reports/vessel_construction_report.xlsx
@@ -639,11 +639,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="546" customWidth="1" min="1" max="1"/>
-    <col width="145" customWidth="1" min="2" max="2"/>
+    <col width="262" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -1607,6 +1607,18 @@
       <c r="B42" s="25" t="inlineStr">
         <is>
           <t>Audit outfitting contracts, renegotiate rates, freeze non-essential VOs, and reallocate welding capacity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="24" t="inlineStr">
+        <is>
+          <t>Completion Status:</t>
+        </is>
+      </c>
+      <c r="B43" s="25" t="inlineStr">
+        <is>
+          <t>Project is overall at 99.5% physical progress. WBS 1.0 (Project Management &amp; Engineering) is at 97.5% due to outstanding closeout docs, final as-built drawing revisions, and class approval compilation. All other WBS packages (2.0, 3.0, 4.0) are 100% complete.</t>
         </is>
       </c>
     </row>
